--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>321600</v>
+      </c>
+      <c r="E8" s="3">
         <v>328100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>354200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>356600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>323500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>245400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>316800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>415700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E9" s="3">
         <v>286700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>303200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>302900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>283100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>265700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>311200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>334300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E10" s="3">
         <v>41400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>40400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-20300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>81400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,8 +884,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -882,22 +902,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>11400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +948,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>295200</v>
+      </c>
+      <c r="E17" s="3">
         <v>309700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>323400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>320700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>315600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>282500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>329400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>382900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E18" s="3">
         <v>18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>35900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-37100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,153 +1039,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>32800</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>43800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E21" s="3">
         <v>18600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>49200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>33400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>600</v>
       </c>
       <c r="F22" s="3">
         <v>600</v>
       </c>
       <c r="G22" s="3">
+        <v>600</v>
+      </c>
+      <c r="H22" s="3">
         <v>700</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>76000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>74500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>28900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>74500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E32" s="3">
         <v>13900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-32800</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-43800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>74500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>74500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>278100</v>
+      </c>
+      <c r="E41" s="3">
         <v>280600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>225400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>221900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>227400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>257200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>262500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>238500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,124 +1678,139 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E43" s="3">
         <v>113200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>133300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>79400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>159900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>237500</v>
+      </c>
+      <c r="E44" s="3">
         <v>228000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>255400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>266000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>244700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>192400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>205600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>261800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E45" s="3">
         <v>35000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>647700</v>
+      </c>
+      <c r="E46" s="3">
         <v>656800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>630500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>626700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>614700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>556600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>582500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>669600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,66 +1838,75 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>502500</v>
+      </c>
+      <c r="E48" s="3">
         <v>503900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>498800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>496900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>495100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>498600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>499100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>502900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1165800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1175300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1153800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1148500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1135300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1082000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1122300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1217300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,37 +2092,41 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>145400</v>
+      </c>
+      <c r="E57" s="3">
         <v>133300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>148500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>164600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>173300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>113200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>187500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2000,7 +2134,7 @@
         <v>13200</v>
       </c>
       <c r="E58" s="3">
-        <v>13100</v>
+        <v>13200</v>
       </c>
       <c r="F58" s="3">
         <v>13100</v>
@@ -2009,7 +2143,7 @@
         <v>13100</v>
       </c>
       <c r="H58" s="3">
-        <v>20400</v>
+        <v>13100</v>
       </c>
       <c r="I58" s="3">
         <v>20400</v>
@@ -2018,68 +2152,77 @@
         <v>20400</v>
       </c>
       <c r="K58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="L58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E59" s="3">
         <v>101900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>53100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>239100</v>
+      </c>
+      <c r="E60" s="3">
         <v>248400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>207000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>219800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>231000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>186700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>191900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>260000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2107,37 +2250,43 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E62" s="3">
         <v>195300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>216500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>216900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>212900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>208800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>195300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>188400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>426500</v>
+      </c>
+      <c r="E66" s="3">
         <v>443700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>423500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>436700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>443900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>395500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>387200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>448400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-53700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-79800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-108700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-123100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-89900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-76600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>739300</v>
+      </c>
+      <c r="E76" s="3">
         <v>731600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>730300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>711800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>691400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>686500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>735100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>768900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>74500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E83" s="3">
         <v>14100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E89" s="3">
         <v>74100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>50700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3209,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3239,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3335,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3399,39 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>55000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>23700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,161 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>294700</v>
+      </c>
+      <c r="E8" s="3">
         <v>321600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>328100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>354200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>356600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>323500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>245400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>316800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>415700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E9" s="3">
         <v>271000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>286700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>303200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>302900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>265700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>311200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>334300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E10" s="3">
         <v>50600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>51000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>53700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>40400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-20300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +904,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -905,22 +925,25 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>11400</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>26400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +974,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +988,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>291500</v>
+      </c>
+      <c r="E17" s="3">
         <v>295200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>309700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>323400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>320700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>315600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>282500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>329400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>382900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E18" s="3">
         <v>26400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-37100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,168 +1073,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>32800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>43800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E21" s="3">
         <v>44000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>49200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>33400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>91300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>600</v>
       </c>
       <c r="G22" s="3">
         <v>600</v>
       </c>
       <c r="H22" s="3">
+        <v>600</v>
+      </c>
+      <c r="I22" s="3">
         <v>700</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>30000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>76000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1281,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E26" s="3">
         <v>24000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>28900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>74500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E27" s="3">
         <v>24000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>28900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>74500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1491,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-32800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-43800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E33" s="3">
         <v>24000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>74500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1596,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E35" s="3">
         <v>24000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>74500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1703,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>272800</v>
+      </c>
+      <c r="E41" s="3">
         <v>278100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>280600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>225400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>221900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>227400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>257200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>262500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>238500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,136 +1771,151 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E43" s="3">
         <v>120000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>133300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>159900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>203900</v>
+      </c>
+      <c r="E44" s="3">
         <v>237500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>228000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>255400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>266000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>244700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>192400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>205600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>261800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E45" s="3">
         <v>12100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>606800</v>
+      </c>
+      <c r="E46" s="3">
         <v>647700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>656800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>630500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>626700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>614700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>556600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>582500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>669600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,72 +1946,81 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>501300</v>
+      </c>
+      <c r="E48" s="3">
         <v>502500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>503900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>498800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>496900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>495100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>498600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>499100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>502900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>13000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1120400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1165800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1175300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1153800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1148500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1135300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1082000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1122300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1217300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,40 +2223,44 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E57" s="3">
         <v>145400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>133300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>148500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>164600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>173300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>113200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>187500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2137,7 +2271,7 @@
         <v>13200</v>
       </c>
       <c r="F58" s="3">
-        <v>13100</v>
+        <v>13200</v>
       </c>
       <c r="G58" s="3">
         <v>13100</v>
@@ -2146,7 +2280,7 @@
         <v>13100</v>
       </c>
       <c r="I58" s="3">
-        <v>20400</v>
+        <v>13100</v>
       </c>
       <c r="J58" s="3">
         <v>20400</v>
@@ -2155,74 +2289,83 @@
         <v>20400</v>
       </c>
       <c r="L58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="M58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E59" s="3">
         <v>80500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>101900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>42100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>195300</v>
+      </c>
+      <c r="E60" s="3">
         <v>239100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>248400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>207000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>219800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>231000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>186700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>191900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>260000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2253,40 +2396,46 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E62" s="3">
         <v>187400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>195300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>216500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>216900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>212900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>208800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>195300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>188400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>384100</v>
+      </c>
+      <c r="E66" s="3">
         <v>426500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>443700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>423500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>436700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>443900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>395500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>387200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>448400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-29700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-53700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-79800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-108700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-123100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-89900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>736300</v>
+      </c>
+      <c r="E76" s="3">
         <v>739300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>731600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>730300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>711800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>691400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>686500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>735100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>768900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2936,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E81" s="3">
         <v>24000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>74500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,8 +3028,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2839,31 +3038,34 @@
         <v>13400</v>
       </c>
       <c r="E83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F83" s="3">
         <v>14100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E89" s="3">
         <v>33400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>50700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3443,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3476,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3581,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3651,42 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>55000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>23700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>227200</v>
+      </c>
+      <c r="E8" s="3">
         <v>294700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>321600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>328100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>354200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>356600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>323500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>245400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>316800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>415700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>215100</v>
+      </c>
+      <c r="E9" s="3">
         <v>270600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>271000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>286700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>303200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>302900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>283100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>265700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>311200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>334300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E10" s="3">
         <v>24100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>51000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>53700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-20300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>81400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,66 +924,72 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-19700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I14" s="3">
-        <v>11400</v>
+        <v>-4100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>26400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>13400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>13400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1015,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>291500</v>
+        <v>236300</v>
       </c>
       <c r="E17" s="3">
-        <v>295200</v>
+        <v>290900</v>
       </c>
       <c r="F17" s="3">
-        <v>309700</v>
+        <v>294500</v>
       </c>
       <c r="G17" s="3">
-        <v>323400</v>
+        <v>347400</v>
       </c>
       <c r="H17" s="3">
-        <v>320700</v>
+        <v>321500</v>
       </c>
       <c r="I17" s="3">
-        <v>315600</v>
+        <v>322500</v>
       </c>
       <c r="J17" s="3">
+        <v>305100</v>
+      </c>
+      <c r="K17" s="3">
         <v>282500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>329400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>382900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3200</v>
+        <v>-9100</v>
       </c>
       <c r="E18" s="3">
-        <v>26400</v>
+        <v>3800</v>
       </c>
       <c r="F18" s="3">
+        <v>27100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>32700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>34100</v>
+      </c>
+      <c r="J18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
-        <v>30800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>35900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,78 +1107,85 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3600</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>4200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>-13900</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>4400</v>
+        <v>-1200</v>
       </c>
       <c r="H20" s="3">
-        <v>4600</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>32800</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>43800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>20200</v>
+        <v>4200</v>
       </c>
       <c r="E21" s="3">
-        <v>44000</v>
+        <v>17300</v>
       </c>
       <c r="F21" s="3">
-        <v>18600</v>
+        <v>40700</v>
       </c>
       <c r="G21" s="3">
-        <v>49200</v>
+        <v>-4000</v>
       </c>
       <c r="H21" s="3">
-        <v>54800</v>
+        <v>46500</v>
       </c>
       <c r="I21" s="3">
-        <v>33400</v>
+        <v>48400</v>
       </c>
       <c r="J21" s="3">
+        <v>32900</v>
+      </c>
+      <c r="K21" s="3">
         <v>10300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>91300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1153,104 +1193,113 @@
         <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>600</v>
       </c>
       <c r="H22" s="3">
         <v>600</v>
       </c>
       <c r="I22" s="3">
+        <v>600</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E23" s="3">
         <v>6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>39900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>76000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>4600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>74500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E27" s="3">
         <v>4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>74500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1561,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3600</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>-4200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>13900</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>-4400</v>
+        <v>1200</v>
       </c>
       <c r="H32" s="3">
-        <v>-4600</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-32800</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-43800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
         <v>4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>74500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
         <v>4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>74500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,43 +1790,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>254600</v>
+      </c>
+      <c r="E41" s="3">
         <v>272800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>278100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>280600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>221900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>227400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>257200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>262500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>238500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,171 +1864,186 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E43" s="3">
         <v>107000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>135800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>133300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>159900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E44" s="3">
         <v>203900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>237500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>228000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>255400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>266000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>244700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>192400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>205600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>261800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23100</v>
+        <v>23000</v>
       </c>
       <c r="E45" s="3">
-        <v>12100</v>
+        <v>22500</v>
       </c>
       <c r="F45" s="3">
-        <v>35000</v>
+        <v>11600</v>
       </c>
       <c r="G45" s="3">
-        <v>13900</v>
+        <v>34300</v>
       </c>
       <c r="H45" s="3">
-        <v>5500</v>
+        <v>13000</v>
       </c>
       <c r="I45" s="3">
-        <v>15500</v>
+        <v>4600</v>
       </c>
       <c r="J45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K45" s="3">
         <v>27600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E46" s="3">
         <v>606800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>647700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>656800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>630500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>626700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>614700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>556600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>582500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>669600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1949,78 +2054,87 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>507900</v>
+      </c>
+      <c r="E48" s="3">
         <v>501300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>502500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>503900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>498800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>496900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>495100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>498600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>499100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>502900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2206,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1133400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1120400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1165800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1175300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1153800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1148500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1135300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1082000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1122300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1217300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,66 +2354,70 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E57" s="3">
         <v>114200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>145400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>133300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>148500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>164600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>173300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>113200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>123800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>187500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13200</v>
+        <v>18300</v>
       </c>
       <c r="E58" s="3">
-        <v>13200</v>
+        <v>17900</v>
       </c>
       <c r="F58" s="3">
-        <v>13200</v>
+        <v>17600</v>
       </c>
       <c r="G58" s="3">
-        <v>13100</v>
+        <v>18200</v>
       </c>
       <c r="H58" s="3">
-        <v>13100</v>
+        <v>18500</v>
       </c>
       <c r="I58" s="3">
-        <v>13100</v>
+        <v>18900</v>
       </c>
       <c r="J58" s="3">
-        <v>20400</v>
+        <v>19000</v>
       </c>
       <c r="K58" s="3">
         <v>20400</v>
@@ -2292,103 +2426,112 @@
         <v>20400</v>
       </c>
       <c r="M58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="N58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>67900</v>
+        <v>59000</v>
       </c>
       <c r="E59" s="3">
-        <v>80500</v>
+        <v>22500</v>
       </c>
       <c r="F59" s="3">
-        <v>101900</v>
+        <v>30100</v>
       </c>
       <c r="G59" s="3">
-        <v>45400</v>
+        <v>26600</v>
       </c>
       <c r="H59" s="3">
-        <v>42100</v>
+        <v>17400</v>
       </c>
       <c r="I59" s="3">
-        <v>44600</v>
+        <v>13800</v>
       </c>
       <c r="J59" s="3">
+        <v>19800</v>
+      </c>
+      <c r="K59" s="3">
         <v>53100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E60" s="3">
         <v>195300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>239100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>248400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>207000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>219800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>231000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>186700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>191900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>260000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2399,43 +2542,49 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>188800</v>
+        <v>13700</v>
       </c>
       <c r="E62" s="3">
-        <v>187400</v>
+        <v>13100</v>
       </c>
       <c r="F62" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G62" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H62" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>16300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>208800</v>
+      </c>
+      <c r="L62" s="3">
         <v>195300</v>
       </c>
-      <c r="G62" s="3">
-        <v>216500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>216900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>212900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>208800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>195300</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>188400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>420700</v>
+      </c>
+      <c r="E66" s="3">
         <v>384100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>426500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>443700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>423500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>436700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>443900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>395500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>387200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>448400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-25100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-29700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-53700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-55000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-108700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-123100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-89900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-76600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>712700</v>
+      </c>
+      <c r="E76" s="3">
         <v>736300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>739300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>731600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>730300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>711800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>691400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>686500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>735100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>768900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
         <v>4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>74500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3227,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13400</v>
+        <v>14000</v>
       </c>
       <c r="E83" s="3">
-        <v>13400</v>
+        <v>14300</v>
       </c>
       <c r="F83" s="3">
-        <v>14100</v>
+        <v>14500</v>
       </c>
       <c r="G83" s="3">
-        <v>14000</v>
+        <v>11800</v>
       </c>
       <c r="H83" s="3">
-        <v>14300</v>
+        <v>14400</v>
       </c>
       <c r="I83" s="3">
-        <v>14500</v>
+        <v>14700</v>
       </c>
       <c r="J83" s="3">
         <v>14600</v>
       </c>
       <c r="K83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="L83" s="3">
         <v>14400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E89" s="3">
         <v>8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>33400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>50700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3509,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,31 +3677,32 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,66 +3827,72 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-48700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3654,39 +3903,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>55000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,187 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>240500</v>
+      </c>
+      <c r="E8" s="3">
         <v>227200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>294700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>321600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>328100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>354200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>356600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>323500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>245400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>316800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>415700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>229600</v>
+      </c>
+      <c r="E9" s="3">
         <v>215100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>270600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>271000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>286700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>303200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>302900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>283100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>265700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>311200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>334300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E10" s="3">
         <v>12100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>53700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-20300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,73 +943,79 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-19700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>26400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E15" s="3">
         <v>13600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>13400</v>
       </c>
       <c r="F15" s="3">
         <v>13400</v>
       </c>
       <c r="G15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H15" s="3">
         <v>14100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1003,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>256900</v>
+      </c>
+      <c r="E17" s="3">
         <v>236300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>290900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>294500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>347400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>321500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>322500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>305100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>282500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>329400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>382900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,198 +1140,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>32800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>43800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
       </c>
       <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>600</v>
       </c>
       <c r="I22" s="3">
         <v>600</v>
       </c>
       <c r="J22" s="3">
+        <v>600</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>39900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>76000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>74500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>74500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-32800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-43800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>240700</v>
+      </c>
+      <c r="E41" s="3">
         <v>254600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>272800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>278100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>280600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>221900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>227400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>257200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>262500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>238500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,160 +1956,175 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E43" s="3">
         <v>105100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>107000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>135800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>133300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>127100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>159900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>219800</v>
+      </c>
+      <c r="E44" s="3">
         <v>218000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>203900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>237500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>228000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>255400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>266000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>244700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>192400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>205600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>261800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E45" s="3">
         <v>23000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>587300</v>
+      </c>
+      <c r="E46" s="3">
         <v>602000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>606800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>647700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>656800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>630500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>626700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>614700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>556600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>582500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>669600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2045,8 +2149,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2057,84 +2161,93 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E48" s="3">
         <v>507900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>501300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>502500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>503900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>498800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>496900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>495100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>498600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>499100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>502900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>4000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E52" s="3">
         <v>19500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1116700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1133400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1120400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1165800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1175300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1153800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1148500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1135300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1082000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1122300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1217300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,72 +2484,76 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>119200</v>
+      </c>
+      <c r="E57" s="3">
         <v>113300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>114200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>145400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>133300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>148500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>164600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>173300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>113200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>123800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>187500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E58" s="3">
         <v>18300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>20400</v>
       </c>
       <c r="L58" s="3">
         <v>20400</v>
@@ -2429,113 +2562,122 @@
         <v>20400</v>
       </c>
       <c r="N58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="O58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E59" s="3">
         <v>59000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>53100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>281500</v>
+      </c>
+      <c r="E60" s="3">
         <v>228200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>195300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>239100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>248400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>219800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>231000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>186700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>191900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>260000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E61" s="3">
         <v>6500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2545,46 +2687,52 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E62" s="3">
         <v>13700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>208800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>195300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>188400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>426200</v>
+      </c>
+      <c r="E66" s="3">
         <v>420700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>384100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>426500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>443700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>423500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>436700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>443900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>395500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>387200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>448400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-31000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-25100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-53700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-55000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-108700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-123100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-89900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-76600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>690500</v>
+      </c>
+      <c r="E76" s="3">
         <v>712700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>736300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>739300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>731600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>730300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>711800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>691400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>686500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>735100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>768900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>14600</v>
       </c>
       <c r="K83" s="3">
         <v>14600</v>
       </c>
       <c r="L83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="M83" s="3">
         <v>14400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>33400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>50700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>17900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3704,8 +3937,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3716,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3894,8 +4142,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3906,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>280500</v>
+      </c>
+      <c r="E8" s="3">
         <v>240500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>227200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>294700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>321600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>328100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>354200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>356600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>323500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>245400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>316800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>415700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E9" s="3">
         <v>229600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>215100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>270600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>271000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>286700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>303200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>302900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>283100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>265700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>311200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>334300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E10" s="3">
         <v>10900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>53700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>40400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-20300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,49 +963,55 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>9600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-19700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>26400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -996,29 +1019,29 @@
         <v>13700</v>
       </c>
       <c r="E15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F15" s="3">
         <v>13600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>13400</v>
       </c>
       <c r="G15" s="3">
         <v>13400</v>
       </c>
       <c r="H15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I15" s="3">
         <v>14100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>281500</v>
+      </c>
+      <c r="E17" s="3">
         <v>256900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>236300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>290900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>294500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>347400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>321500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>322500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>305100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>282500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>329400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>382900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-16400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,90 +1174,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>32800</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>43800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>91300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1232,122 +1272,131 @@
         <v>500</v>
       </c>
       <c r="E22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
       </c>
       <c r="G22" s="3">
+        <v>700</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>600</v>
       </c>
       <c r="J22" s="3">
         <v>600</v>
       </c>
       <c r="K22" s="3">
+        <v>600</v>
+      </c>
+      <c r="L22" s="3">
         <v>700</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>76000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>74500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>74500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-32800</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-43800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180300</v>
+      </c>
+      <c r="E41" s="3">
         <v>240700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>254600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>272800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>278100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>280600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>221900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>227400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>257200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>262500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>238500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,172 +2049,187 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E43" s="3">
         <v>90800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>105100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>133300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>127100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>159900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E44" s="3">
         <v>219800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>218000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>203900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>237500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>228000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>255400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>266000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>244700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>192400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>205600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>261800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E45" s="3">
         <v>34800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>568400</v>
+      </c>
+      <c r="E46" s="3">
         <v>587300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>602000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>606800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>647700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>656800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>630500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>626700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>614700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>556600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>582500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>669600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2152,8 +2257,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2164,90 +2269,99 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>520800</v>
+      </c>
+      <c r="E48" s="3">
         <v>519000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>507900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>501300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>502500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>503900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>498800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>496900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>495100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>498600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>499100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>502900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1101500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1116700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1133400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1120400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1165800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1175300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1153800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1148500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1135300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1082000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1122300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1217300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,78 +2615,82 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E57" s="3">
         <v>119200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>113300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>145400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>133300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>148500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>164600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>173300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>113200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>123800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>187500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E58" s="3">
         <v>10200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>20400</v>
       </c>
       <c r="M58" s="3">
         <v>20400</v>
@@ -2565,122 +2699,131 @@
         <v>20400</v>
       </c>
       <c r="O58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="P58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E59" s="3">
         <v>68800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>53100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>280100</v>
+      </c>
+      <c r="E60" s="3">
         <v>281500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>228200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>195300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>239100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>248400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>207000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>219800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>231000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>186700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>191900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>260000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E61" s="3">
         <v>6900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2690,49 +2833,55 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E62" s="3">
         <v>13300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>208800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>195300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>188400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>415400</v>
+      </c>
+      <c r="E66" s="3">
         <v>426200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>420700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>384100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>426500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>443700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>423500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>436700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>443900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>395500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>387200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>448400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-52400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-25100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-53700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-55000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-108700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-123100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-89900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-76600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>686100</v>
+      </c>
+      <c r="E76" s="3">
         <v>690500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>712700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>736300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>739300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>731600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>730300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>711800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>691400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>686500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>735100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>768900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E83" s="3">
         <v>11800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>14600</v>
       </c>
       <c r="L83" s="3">
         <v>14600</v>
       </c>
       <c r="M83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N83" s="3">
         <v>14400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E89" s="3">
         <v>13900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>33400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>50700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3940,8 +4174,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-30200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4145,8 +4394,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-29500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>304600</v>
+      </c>
+      <c r="E8" s="3">
         <v>280500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>240500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>227200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>294700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>321600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>328100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>354200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>356600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>323500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>245400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>316800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>415700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>272400</v>
+      </c>
+      <c r="E9" s="3">
         <v>258600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>229600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>215100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>270600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>271000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>286700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>303200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>302900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>283100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>265700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>311200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>334300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E10" s="3">
         <v>21900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>53700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-20300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,85 +983,91 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-19700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13700</v>
+        <v>14100</v>
       </c>
       <c r="E15" s="3">
         <v>13700</v>
       </c>
       <c r="F15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="G15" s="3">
         <v>13600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>13400</v>
       </c>
       <c r="H15" s="3">
         <v>13400</v>
       </c>
       <c r="I15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J15" s="3">
         <v>14100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14500</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E17" s="3">
         <v>281500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>256900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>236300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>290900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>294500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>347400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>321500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>322500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>305100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>282500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>329400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>382900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,228 +1208,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32800</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>43800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E21" s="3">
         <v>13600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>40700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>91300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
         <v>500</v>
       </c>
       <c r="F22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G22" s="3">
         <v>700</v>
       </c>
       <c r="H22" s="3">
+        <v>700</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>600</v>
       </c>
       <c r="K22" s="3">
         <v>600</v>
       </c>
       <c r="L22" s="3">
+        <v>600</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>39900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>74500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32800</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-43800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2050,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>190800</v>
+      </c>
+      <c r="E41" s="3">
         <v>180300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>240700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>254600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>272800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>278100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>280600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>225400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>221900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>227400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>257200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>262500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>238500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,184 +2142,199 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E43" s="3">
         <v>125700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>90800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>107000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>135800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>133300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>127100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>159900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E44" s="3">
         <v>230600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>219800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>218000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>203900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>237500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>228000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>255400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>266000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>244700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>192400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>205600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>261800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E45" s="3">
         <v>30200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>560500</v>
+      </c>
+      <c r="E46" s="3">
         <v>568400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>587300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>602000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>606800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>647700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>656800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>630500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>626700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>614700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>556600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>582500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>669600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2260,8 +2365,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2272,96 +2377,105 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>539100</v>
+      </c>
+      <c r="E48" s="3">
         <v>520800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>519000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>507900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>501300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>502500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>503900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>498800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>496900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>495100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>498600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>499100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>502900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E52" s="3">
         <v>9000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1101500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1116700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1133400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1120400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1165800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1175300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1153800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1148500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1135300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1082000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1122300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1217300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,84 +2746,88 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E57" s="3">
         <v>143300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>119200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>113300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>114200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>145400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>164600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>173300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>113200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>123800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>187500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>9500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>20400</v>
       </c>
       <c r="N58" s="3">
         <v>20400</v>
@@ -2702,131 +2836,140 @@
         <v>20400</v>
       </c>
       <c r="P58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E59" s="3">
         <v>82000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>30100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>53100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>52100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E60" s="3">
         <v>280100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>281500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>228200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>195300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>239100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>248400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>207000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>219800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>231000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>186700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>191900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>260000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E61" s="3">
         <v>6100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2836,52 +2979,58 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E62" s="3">
         <v>12700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>208800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>195300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>188400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>422000</v>
+      </c>
+      <c r="E66" s="3">
         <v>415400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>426200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>420700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>384100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>426500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>443700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>423500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>436700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>443900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>395500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>387200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>448400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-53700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-108700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-123100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-89900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E76" s="3">
         <v>686100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>690500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>712700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>736300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>739300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>731600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>730300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>711800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>691400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>686500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>735100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>768900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,43 +3833,46 @@
         <v>13400</v>
       </c>
       <c r="E83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F83" s="3">
         <v>11800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>14600</v>
       </c>
       <c r="M83" s="3">
         <v>14600</v>
       </c>
       <c r="N83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="O83" s="3">
         <v>14400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-38900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>50700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4177,8 +4411,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4564,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-20100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-20300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-48700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4397,8 +4646,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-60000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>267300</v>
+      </c>
+      <c r="E8" s="3">
         <v>305900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>304600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>280500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>240500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>227200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>294700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>321600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>328100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>354200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>356600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>323500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>245400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>316800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>415700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E9" s="3">
         <v>270900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>272400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>258600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>229600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>215100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>270600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>271000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>286700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>303200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>302900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>283100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>265700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>311200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>334300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E10" s="3">
         <v>35000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>32200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>50600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>51000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>53700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-20300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,97 +1022,103 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-19700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E15" s="3">
         <v>14300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>13700</v>
       </c>
       <c r="G15" s="3">
         <v>13700</v>
       </c>
       <c r="H15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I15" s="3">
         <v>13600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>13400</v>
       </c>
       <c r="J15" s="3">
         <v>13400</v>
       </c>
       <c r="K15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="L15" s="3">
         <v>14100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14500</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>288700</v>
+      </c>
+      <c r="E17" s="3">
         <v>293900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>293800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>281500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>256900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>236300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>290900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>294500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>347400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>321500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>322500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>305100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>282500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>329400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>382900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E18" s="3">
         <v>12000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,258 +1275,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>32800</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>43800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>26700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>25000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>48400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>91300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>600</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>500</v>
       </c>
       <c r="G22" s="3">
         <v>500</v>
       </c>
       <c r="H22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I22" s="3">
         <v>700</v>
       </c>
       <c r="J22" s="3">
+        <v>700</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>600</v>
       </c>
       <c r="M22" s="3">
         <v>600</v>
       </c>
       <c r="N22" s="3">
+        <v>600</v>
+      </c>
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E23" s="3">
         <v>10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>30000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>39900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>76000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>74500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E27" s="3">
         <v>8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-32800</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-43800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E33" s="3">
         <v>8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-33200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E35" s="3">
         <v>8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-33200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>156700</v>
+      </c>
+      <c r="E41" s="3">
         <v>191500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>190800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>180300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>240700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>254600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>272800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>278100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>280600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>225400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>221900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>227400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>257200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>262500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>238500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,208 +2327,223 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E43" s="3">
         <v>129300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>129600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>125700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>105100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>107000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>133300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>127100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>159900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>243200</v>
+      </c>
+      <c r="E44" s="3">
         <v>237500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>223400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>230600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>219800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>218000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>203900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>237500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>228000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>255400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>266000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>244700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>192400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>205600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>261800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E45" s="3">
         <v>20600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>553200</v>
+      </c>
+      <c r="E46" s="3">
         <v>579600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>560500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>568400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>587300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>602000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>606800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>647700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>656800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>630500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>626700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>614700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>556600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>582500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>669600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2476,8 +2580,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2488,108 +2592,117 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>577400</v>
+      </c>
+      <c r="E48" s="3">
         <v>558800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>539100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>520800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>519000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>507900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>501300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>502500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>503900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>498800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>496900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>495100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>498600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>499100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>502900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E49" s="3">
         <v>3100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,58 +2804,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
         <v>8900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>39000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1140200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1150400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1112000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1101500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1116700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1133400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1120400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1165800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1175300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1153800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1148500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1135300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1082000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1122300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1217300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,96 +3007,100 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E57" s="3">
         <v>155200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>143700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>143300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>119200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>113300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>114200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>145400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>133300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>148500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>164600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>173300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>113200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>123800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>187500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="E58" s="3">
         <v>5100</v>
       </c>
       <c r="F58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G58" s="3">
         <v>9500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>20400</v>
       </c>
       <c r="P58" s="3">
         <v>20400</v>
@@ -2976,149 +3109,158 @@
         <v>20400</v>
       </c>
       <c r="R58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="S58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E59" s="3">
         <v>102600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>87500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>59000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>53100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>52100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E60" s="3">
         <v>305400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>276200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>280100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>281500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>228200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>195300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>239100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>248400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>207000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>219800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>231000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>186700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>191900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>260000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E61" s="3">
         <v>10600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3128,58 +3270,64 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E62" s="3">
         <v>12200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>208800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>195300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>188400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>454200</v>
+      </c>
+      <c r="E66" s="3">
         <v>452700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>422000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>415400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>426200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>420700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>384100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>426500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>443700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>423500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>436700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>443900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>395500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>387200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>448400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-47400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-52400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-53700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-55000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-79800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-108700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-123100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-89900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-76600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>686000</v>
+      </c>
+      <c r="E76" s="3">
         <v>697700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>690000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>686100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>690500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>712700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>736300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>739300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>731600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>730300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>711800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>691400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>686500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>735100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>768900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E81" s="3">
         <v>8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-33200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E83" s="3">
         <v>13600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>13400</v>
       </c>
       <c r="F83" s="3">
         <v>13400</v>
       </c>
       <c r="G83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>14600</v>
       </c>
       <c r="O83" s="3">
         <v>14600</v>
       </c>
       <c r="P83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>14400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>22000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-38900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>23700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>46800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>50700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4651,8 +4884,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-30200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4901,8 +5149,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4913,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-60000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-29500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>MTUS</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>308300</v>
+      </c>
+      <c r="E8" s="3">
         <v>267300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>305900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>304600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>280500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>240500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>227200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>294700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>321600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>328100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>354200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>356600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>323500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>245400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>316800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>415700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>352000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>283200</v>
+      </c>
+      <c r="E9" s="3">
         <v>261300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>270900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>272400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>258600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>229600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>215100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>270600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>271000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>286700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>303200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>302900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>283100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>265700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>311200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>334300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E10" s="3">
         <v>6000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>35000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>41400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>51000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>53700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>40400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,103 +1042,109 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-19700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E15" s="3">
         <v>14500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>13700</v>
       </c>
       <c r="H15" s="3">
         <v>13700</v>
       </c>
       <c r="I15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J15" s="3">
         <v>13600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>13400</v>
       </c>
       <c r="K15" s="3">
         <v>13400</v>
       </c>
       <c r="L15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="M15" s="3">
         <v>14100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14500</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300700</v>
+      </c>
+      <c r="E17" s="3">
         <v>288700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>293900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>293800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>281500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>256900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>236300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>290900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>294500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>347400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>321500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>322500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>305100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>282500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>329400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>382900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1285,264 +1319,279 @@
         <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>32800</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>43800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>91300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>53800</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>500</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J22" s="3">
         <v>700</v>
       </c>
       <c r="K22" s="3">
+        <v>700</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>600</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
       </c>
       <c r="O22" s="3">
+        <v>600</v>
+      </c>
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>30000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>39900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>76000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>74500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1921,105 +1991,111 @@
         <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-43800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E41" s="3">
         <v>156700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>191500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>190800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>180300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>240700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>254600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>272800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>278100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>280600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>225400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>221900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>227400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>257200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>262500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>238500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,220 +2420,235 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E43" s="3">
         <v>126000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>129300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>129600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>125700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>90800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>135800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>133300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>127100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>79400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>159900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>135100</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E44" s="3">
         <v>243200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>237500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>223400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>230600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>219800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>218000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>203900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>237500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>228000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>255400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>266000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>244700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>192400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>205600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>261800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E45" s="3">
         <v>26500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E46" s="3">
         <v>553200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>579600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>560500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>568400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>587300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>602000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>606800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>647700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>656800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>630500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>626700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>614700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>556600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>582500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>669600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>615200</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2583,8 +2688,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2595,114 +2700,123 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>574900</v>
+      </c>
+      <c r="E48" s="3">
         <v>577400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>558800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>539100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>520800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>519000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>507900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>501300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>502500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>503900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>498800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>496900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>495100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>498600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>499100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>502900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>514600</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>39000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1138200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1140200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1150400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1112000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1101500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1116700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1133400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1120400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1165800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1175300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1153800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1148500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1135300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1082000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1122300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1217300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1186000</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,102 +3138,106 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E57" s="3">
         <v>151100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>155200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>143700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>143300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>119200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>113300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>114200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>145400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>133300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>148500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>164600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>173300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>113200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>123800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>187500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>168500</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5100</v>
       </c>
       <c r="F58" s="3">
         <v>5100</v>
       </c>
       <c r="G58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H58" s="3">
         <v>9500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>20400</v>
       </c>
       <c r="Q58" s="3">
         <v>20400</v>
@@ -3112,158 +3246,167 @@
         <v>20400</v>
       </c>
       <c r="S58" s="3">
+        <v>20400</v>
+      </c>
+      <c r="T58" s="3">
         <v>35200</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E59" s="3">
         <v>103200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>102600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>87500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>59000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>53100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>47700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>52100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E60" s="3">
         <v>314900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>305400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>276200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>280100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>281500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>228200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>195300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>239100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>248400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>207000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>219800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>231000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>186700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>191900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>260000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>246200</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E61" s="3">
         <v>10100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3273,61 +3416,67 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E62" s="3">
         <v>12100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>208800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>195300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>188400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>236600</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>455200</v>
+      </c>
+      <c r="E66" s="3">
         <v>454200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>452700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>422000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>415400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>426200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>420700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>384100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>426500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>443700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>423500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>436700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>443900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>395500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>387200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>448400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>482800</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-53600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-47400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-51100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-29700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-53700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-79800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-123100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-89900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-76600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-151100</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>683000</v>
+      </c>
+      <c r="E76" s="3">
         <v>686000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>697700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>690000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>686100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>690500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>712700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>736300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>739300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>731600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>730300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>711800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>691400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>686500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>735100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>768900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>703200</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37100</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E83" s="3">
         <v>12000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>13400</v>
       </c>
       <c r="G83" s="3">
         <v>13400</v>
       </c>
       <c r="H83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I83" s="3">
         <v>11800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>14600</v>
       </c>
       <c r="P83" s="3">
         <v>14600</v>
       </c>
       <c r="Q83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="R83" s="3">
         <v>14400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-38900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>74100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>46800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>50700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>17900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6500</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4887,8 +5121,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-30200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25500</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5152,8 +5401,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-34700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-60000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>55000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18700</v>
       </c>
     </row>
